--- a/outputs/terminal_value_sensitivity.xlsx
+++ b/outputs/terminal_value_sensitivity.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AG20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -432,9 +432,9 @@
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
@@ -452,9 +452,9 @@
     <col width="21" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
     <col width="16" customWidth="1" min="30" max="30"/>
     <col width="20" customWidth="1" min="31" max="31"/>
     <col width="20" customWidth="1" min="32" max="32"/>
@@ -629,233 +629,233 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>DHT</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>late-cycle/peak</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="F2" t="n">
-        <v>16.00999768916909</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-2.37806287092015</v>
-      </c>
-      <c r="H2" t="n">
-        <v>12.92487836800897</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-21.1897660487258</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>16.1686402432938</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1.41073022381828</v>
-      </c>
-      <c r="M2" t="n">
-        <v>13.06183841049449</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-20.35464383844824</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>16.48592535154322</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.5239350703854617</v>
-      </c>
-      <c r="R2" t="n">
-        <v>13.33575849546553</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-18.68439941789309</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>16.80321045979263</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.458600364589225</v>
-      </c>
-      <c r="W2" t="n">
-        <v>13.60967858043657</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-17.01415499733796</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>16.96185301391734</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.425933011691096</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13.7466386229221</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-16.17903278706036</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>5.773745206599173</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>6.162081108416513</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
+      <c r="F2" s="2" t="n">
+        <v>13.91000661316703</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-15.18288650507905</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>16.83077879715786</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2.626699982669889</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>14.04213671232856</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-14.37721516872829</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>16.99473320090292</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>3.626421956725157</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>14.30639691065161</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-12.76587249602675</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>17.32264200839305</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>5.62586590483567</v>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>14.57065710897466</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>-11.15452982332524</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>17.65055081588317</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>7.625309852946183</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>14.70278720813618</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>-10.34885848697448</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>17.81450521962823</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>8.625031827001406</v>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>5.541441356061478</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>5.678847499092461</v>
+      </c>
+      <c r="AG2" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ECO</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2" t="n">
         <v>47.7</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>late-cycle/peak</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="F3" t="n">
-        <v>41.30708139765617</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-13.40234507828896</v>
-      </c>
-      <c r="H3" t="n">
-        <v>31.49732214101844</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-33.96787811107247</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>41.72629252163875</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-12.52349576176363</v>
-      </c>
-      <c r="M3" t="n">
-        <v>31.84154840004664</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-33.24622976929425</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>42.56471476960392</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-10.76579712871297</v>
-      </c>
-      <c r="R3" t="n">
-        <v>32.53000091810306</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-31.80293308573782</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>43.40313701756908</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-9.00809849566231</v>
-      </c>
-      <c r="W3" t="n">
-        <v>33.21845343615948</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-30.35963640218139</v>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>43.82234814155166</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-8.129249179136988</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>33.56267969518768</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-29.63798806040319</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>5.909276633263561</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>6.349085446904698</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
+      <c r="F3" s="2" t="n">
+        <v>35.64314890676505</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-25.2764173862368</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>44.0930795939319</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-7.56167800014278</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>35.9853928277651</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-24.55892488938134</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>44.53169969867715</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>-6.642138996483959</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>36.66988066976521</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-23.12393989567042</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>45.40893990816763</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>-4.803060989166397</v>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>37.35436851176532</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-21.6889549019595</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>46.28618011765812</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-2.963982981848812</v>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>37.69661243276538</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>-20.97146240510403</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>46.72480022240337</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>-2.044443978190014</v>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>5.599864216884227</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>5.795600235974914</v>
+      </c>
+      <c r="AG3" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -879,95 +879,95 @@
         <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>30.4780530795577</v>
+        <v>26.38746093473351</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.65781716070233</v>
+        <v>-23.51460598627968</v>
       </c>
       <c r="H4" t="n">
-        <v>23.16237270534974</v>
+        <v>32.83454116973007</v>
       </c>
       <c r="I4" t="n">
-        <v>-32.86268781058047</v>
+        <v>-4.827416899333137</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>30.77372772535714</v>
+        <v>26.62327909236339</v>
       </c>
       <c r="L4" t="n">
-        <v>-10.80078920186336</v>
+        <v>-22.83107509459887</v>
       </c>
       <c r="M4" t="n">
-        <v>23.39906817612228</v>
+        <v>33.14567899713411</v>
       </c>
       <c r="N4" t="n">
-        <v>-32.17661398225425</v>
+        <v>-3.925568124248946</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>31.36507701695602</v>
+        <v>27.09491540762314</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9.086733284185444</v>
+        <v>-21.46401331123727</v>
       </c>
       <c r="R4" t="n">
-        <v>23.87245911766737</v>
+        <v>33.76795465194221</v>
       </c>
       <c r="S4" t="n">
-        <v>-30.80446632560183</v>
+        <v>-2.121870574080542</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>31.95642630855491</v>
+        <v>27.56655172288289</v>
       </c>
       <c r="V4" t="n">
-        <v>-7.372677366507519</v>
+        <v>-20.09695152787569</v>
       </c>
       <c r="W4" t="n">
-        <v>24.34585005921246</v>
+        <v>34.3902303067503</v>
       </c>
       <c r="X4" t="n">
-        <v>-29.4323186689494</v>
+        <v>-0.3181730239121605</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>32.25210095435435</v>
+        <v>27.80236988051276</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6.515649407668556</v>
+        <v>-19.41342063619489</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.582545529985</v>
+        <v>34.70136813415436</v>
       </c>
       <c r="AC4" t="n">
-        <v>-28.74624484062319</v>
+        <v>0.5836757511720414</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>5.656124720617128</v>
+        <v>5.222045998273052</v>
       </c>
       <c r="AF4" t="n">
-        <v>5.949000970680171</v>
+        <v>5.52839810307231</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -994,16 +994,16 @@
         <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>40.93027032719714</v>
+        <v>36.23095763209573</v>
       </c>
       <c r="G5" t="n">
-        <v>-47.52529445231135</v>
+        <v>-53.55005431782598</v>
       </c>
       <c r="H5" t="n">
-        <v>50.34289874724699</v>
+        <v>62.59451230693033</v>
       </c>
       <c r="I5" t="n">
-        <v>-35.45782211891412</v>
+        <v>-19.75062524752521</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1011,16 +1011,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>41.34606083771447</v>
+        <v>36.59189452852569</v>
       </c>
       <c r="L5" t="n">
-        <v>-46.99222969523787</v>
+        <v>-53.08731470701834</v>
       </c>
       <c r="M5" t="n">
-        <v>50.92089517977307</v>
+        <v>63.25915276716486</v>
       </c>
       <c r="N5" t="n">
-        <v>-34.71680105157299</v>
+        <v>-18.89852209337839</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42.17764185874911</v>
+        <v>37.31376832138561</v>
       </c>
       <c r="Q5" t="n">
-        <v>-45.92610018109088</v>
+        <v>-52.16183548540306</v>
       </c>
       <c r="R5" t="n">
-        <v>52.0768880448252</v>
+        <v>64.58843368763391</v>
       </c>
       <c r="S5" t="n">
-        <v>-33.23475891689077</v>
+        <v>-17.19431578508474</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>43.00922287978376</v>
+        <v>38.03564211424553</v>
       </c>
       <c r="V5" t="n">
-        <v>-44.85997066694389</v>
+        <v>-51.23635626378778</v>
       </c>
       <c r="W5" t="n">
-        <v>53.23288090987734</v>
+        <v>65.91771460810294</v>
       </c>
       <c r="X5" t="n">
-        <v>-31.75271678220854</v>
+        <v>-15.4901094767911</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1062,16 +1062,16 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>43.42501339030109</v>
+        <v>38.3965790106755</v>
       </c>
       <c r="AA5" t="n">
-        <v>-44.3269059098704</v>
+        <v>-50.77361665298014</v>
       </c>
       <c r="AB5" t="n">
-        <v>53.8108773424034</v>
+        <v>66.58235506833746</v>
       </c>
       <c r="AC5" t="n">
-        <v>-31.01169571486744</v>
+        <v>-14.63800632264428</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1079,128 +1079,128 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>5.914847187186806</v>
+        <v>5.803813112433846</v>
       </c>
       <c r="AF5" t="n">
-        <v>6.659342993328146</v>
+        <v>6.174236676327145</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
         <v>70.8</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>late-cycle/peak</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>0.7</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>0.3</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>76.47522935957812</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>8.015860677370235</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>66.15397298043762</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>-6.562185055879066</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>77.35968325504544</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>9.265089343284515</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>67.20528210858515</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>-5.077285157365596</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>79.12859104598006</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>11.76354667511308</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>69.30790036488023</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>-2.107485360338657</v>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>80.89749883691468</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>14.26200400694164</v>
-      </c>
-      <c r="W6" s="2" t="n">
-        <v>71.4105186211753</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>0.8623144366882718</v>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="n">
-        <v>81.78195273238197</v>
-      </c>
-      <c r="AA6" s="2" t="n">
-        <v>15.5112326728559</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>72.46182774932282</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>2.347214335201731</v>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>6.706455028019155</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>9.101205974609975</v>
-      </c>
-      <c r="AG6" s="2" t="b">
-        <v>1</v>
+      <c r="F6" t="n">
+        <v>71.45356736080865</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9231177412551528</v>
+      </c>
+      <c r="H6" t="n">
+        <v>76.01771000854768</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.369646904728366</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>72.28326103867268</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.095001467051816</v>
+      </c>
+      <c r="M6" t="n">
+        <v>76.97914592156958</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8.72760723385535</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>73.94264839440076</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.438768918645142</v>
+      </c>
+      <c r="R6" t="n">
+        <v>78.9020177476134</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11.44352789210932</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>75.60203575012885</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.78253637023849</v>
+      </c>
+      <c r="W6" t="n">
+        <v>80.82488957365722</v>
+      </c>
+      <c r="X6" t="n">
+        <v>14.15944855036331</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>76.43172942799289</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.954420096035153</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>81.7863254866791</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>15.51740887949027</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>6.732463842289437</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7.311112748198267</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1224,16 +1224,16 @@
         <v>0.3</v>
       </c>
       <c r="F7" t="n">
-        <v>3.022668559327767</v>
+        <v>2.545676830598248</v>
       </c>
       <c r="G7" t="n">
-        <v>-41.87175847446603</v>
+        <v>-51.04467633464908</v>
       </c>
       <c r="H7" t="n">
-        <v>2.234792724899013</v>
+        <v>3.302578315635097</v>
       </c>
       <c r="I7" t="n">
-        <v>-57.02321682886513</v>
+        <v>-36.4888785454789</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3.043753765474872</v>
+        <v>2.561713179567651</v>
       </c>
       <c r="L7" t="n">
-        <v>-41.46627374086786</v>
+        <v>-50.73628500831442</v>
       </c>
       <c r="M7" t="n">
-        <v>2.250246312120566</v>
+        <v>3.325771668006176</v>
       </c>
       <c r="N7" t="n">
-        <v>-56.72603245921988</v>
+        <v>-36.04285253834277</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.085924177769082</v>
+        <v>2.593785877506456</v>
       </c>
       <c r="Q7" t="n">
-        <v>-40.65530427367151</v>
+        <v>-50.11950235564507</v>
       </c>
       <c r="R7" t="n">
-        <v>2.281153486563673</v>
+        <v>3.372158372748335</v>
       </c>
       <c r="S7" t="n">
-        <v>-56.13166371992937</v>
+        <v>-35.15080052407049</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,16 +1275,16 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>3.128094590063292</v>
+        <v>2.625858575445261</v>
       </c>
       <c r="V7" t="n">
-        <v>-39.84433480647516</v>
+        <v>-49.50271970297575</v>
       </c>
       <c r="W7" t="n">
-        <v>2.312060661006779</v>
+        <v>3.418545077490494</v>
       </c>
       <c r="X7" t="n">
-        <v>-55.53729498063886</v>
+        <v>-34.2587485097982</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1292,16 +1292,16 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>3.149179796210397</v>
+        <v>2.641894924414664</v>
       </c>
       <c r="AA7" t="n">
-        <v>-39.43885007287699</v>
+        <v>-49.19432837664108</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.327514248228333</v>
+        <v>3.441738429861573</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55.2401106109936</v>
+        <v>-33.81272250266206</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>4.099622336608719</v>
+        <v>3.709561943829958</v>
       </c>
       <c r="AF7" t="n">
-        <v>4.064677097593949</v>
+        <v>4.126737206386283</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>-17.4618365478412</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>26.47747804635201</v>
+        <v>28.18448464397605</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-10.85024226817505</v>
+        <v>-5.102745306477951</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1362,14 +1362,14 @@
         <v>-15.49599491567466</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26.99880358891413</v>
+        <v>28.70040870559724</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-9.09493741106353</v>
+        <v>-3.365627253881331</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
@@ -1379,14 +1379,14 @@
         <v>-11.56431165134157</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>28.04145467403838</v>
+        <v>29.73225682883964</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>-5.584327696840474</v>
+        <v>0.1086088513119199</v>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="U8" s="2" t="n">
@@ -1396,10 +1396,10 @@
         <v>-7.632628387008489</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>29.08410575916262</v>
+        <v>30.76410495208203</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-2.07371798261744</v>
+        <v>3.58284495650516</v>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         <v>-5.666786754841945</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>29.60543130172474</v>
+        <v>31.28002901370322</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.3184131255059341</v>
+        <v>5.319963009101758</v>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AE8" s="2" t="n">
         <v>13.33743199521123</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>11.15474675523405</v>
+        <v>10.41140061296849</v>
       </c>
       <c r="AG8" s="2" t="b">
         <v>1</v>
@@ -1460,10 +1460,10 @@
         <v>-3.076656768401043</v>
       </c>
       <c r="H9" t="n">
-        <v>24.94814146323756</v>
+        <v>28.07827194394164</v>
       </c>
       <c r="I9" t="n">
-        <v>13.91845417003452</v>
+        <v>28.21128741525865</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>-0.5663418670408094</v>
       </c>
       <c r="M9" t="n">
-        <v>25.44819265621851</v>
+        <v>28.59523237778314</v>
       </c>
       <c r="N9" t="n">
-        <v>16.20179295076947</v>
+        <v>30.57183734147553</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         <v>4.454287935679635</v>
       </c>
       <c r="R9" t="n">
-        <v>26.44829504218042</v>
+        <v>29.62915324546612</v>
       </c>
       <c r="S9" t="n">
-        <v>20.76847051223938</v>
+        <v>35.29293719390922</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         <v>9.47491773840008</v>
       </c>
       <c r="W9" t="n">
-        <v>27.44839742814233</v>
+        <v>30.66307411314909</v>
       </c>
       <c r="X9" t="n">
-        <v>25.33514807370929</v>
+        <v>40.0140370463429</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
         <v>11.9852326397603</v>
       </c>
       <c r="AB9" t="n">
-        <v>27.94844862112328</v>
+        <v>31.18003454699058</v>
       </c>
       <c r="AC9" t="n">
-        <v>27.61848685444424</v>
+        <v>42.37458697255975</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>14.41959895168313</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.34404752026835</v>
+        <v>10.46861709935492</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1569,50 +1569,50 @@
         <v>0.3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>74.65129854226213</v>
+        <v>71.47930927047774</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-1.254896108118875</v>
+        <v>-5.450649113124673</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>70.67150242931311</v>
+        <v>73.32463933673193</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-6.519176680802763</v>
+        <v>-3.009736327074153</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>75.53253130594939</v>
+        <v>72.31871796346391</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.0892443042997404</v>
+        <v>-4.340320154148259</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>71.57942837013351</v>
+        <v>74.34008298970478</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-5.318216441622326</v>
+        <v>-1.666556891924886</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>77.29499683332392</v>
+        <v>73.99753534943626</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>2.242059303338517</v>
+        <v>-2.119662236195408</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>73.3952802517743</v>
+        <v>76.37097029565052</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>-2.916295963261506</v>
+        <v>1.019801978373724</v>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
@@ -1620,16 +1620,16 @@
         </is>
       </c>
       <c r="U10" s="2" t="n">
-        <v>79.05746236069845</v>
+        <v>75.6763527354086</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>4.573362910976786</v>
+        <v>0.1009956817574098</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>75.21113213341511</v>
+        <v>78.40185760159626</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.5143754849006421</v>
+        <v>3.706160848672302</v>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
@@ -1637,27 +1637,27 @@
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>79.93869512438572</v>
+        <v>76.51576142839477</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>5.73901471479592</v>
+        <v>1.211324640733835</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>76.11905807423551</v>
+        <v>79.41730125456914</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0.6865847542797843</v>
+        <v>5.049340283821624</v>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>6.840541818670538</v>
+        <v>6.80624311895463</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>7.422215197264964</v>
+        <v>7.977719667893488</v>
       </c>
       <c r="AG10" s="2" t="b">
         <v>1</v>
@@ -1684,16 +1684,16 @@
         <v>0.3</v>
       </c>
       <c r="F11" t="n">
-        <v>5.544223545562164</v>
+        <v>5.440618881582298</v>
       </c>
       <c r="G11" t="n">
-        <v>-27.99709681088098</v>
+        <v>-29.34261192750262</v>
       </c>
       <c r="H11" t="n">
-        <v>5.255473724595581</v>
+        <v>5.694520398468081</v>
       </c>
       <c r="I11" t="n">
-        <v>-31.74709448577168</v>
+        <v>-26.04518963028467</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1701,16 +1701,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5.59548462692201</v>
+        <v>5.490698507393365</v>
       </c>
       <c r="L11" t="n">
-        <v>-27.33136848153234</v>
+        <v>-28.69222717670955</v>
       </c>
       <c r="M11" t="n">
-        <v>5.307079960078992</v>
+        <v>5.75295945550162</v>
       </c>
       <c r="N11" t="n">
-        <v>-31.07688363533777</v>
+        <v>-25.28624083764129</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>5.698006789641704</v>
+        <v>5.590857759015498</v>
       </c>
       <c r="Q11" t="n">
-        <v>-25.99991182283501</v>
+        <v>-27.3914576751234</v>
       </c>
       <c r="R11" t="n">
-        <v>5.410292431045813</v>
+        <v>5.869837569568698</v>
       </c>
       <c r="S11" t="n">
-        <v>-29.73646193446996</v>
+        <v>-23.76834325235457</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1735,16 +1735,16 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>5.800528952361398</v>
+        <v>5.691017010637631</v>
       </c>
       <c r="V11" t="n">
-        <v>-24.66845516413769</v>
+        <v>-26.09068817353727</v>
       </c>
       <c r="W11" t="n">
-        <v>5.513504902012635</v>
+        <v>5.986715683635775</v>
       </c>
       <c r="X11" t="n">
-        <v>-28.39604023360215</v>
+        <v>-22.25044566706786</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1752,16 +1752,16 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>5.851790033721244</v>
+        <v>5.741096636448697</v>
       </c>
       <c r="AA11" t="n">
-        <v>-24.00272683478904</v>
+        <v>-25.44030342274419</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.565111137496046</v>
+        <v>6.045154740669314</v>
       </c>
       <c r="AC11" t="n">
-        <v>-27.72582938316824</v>
+        <v>-21.4914968744245</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>5.397790833071644</v>
+        <v>5.37444821202731</v>
       </c>
       <c r="AF11" t="n">
-        <v>5.723117869261113</v>
+        <v>5.973493100031332</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1799,212 +1799,1017 @@
         <v>0.3</v>
       </c>
       <c r="F12" t="n">
-        <v>26.49798714208621</v>
+        <v>25.35729248132189</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.035506588346784</v>
+        <v>-10.08052311587981</v>
       </c>
       <c r="H12" t="n">
-        <v>24.82270456143877</v>
+        <v>26.95655144231257</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.976224959437</v>
+        <v>-4.409392048536997</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>26.75531823550216</v>
+        <v>25.60107855780356</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.122984980488798</v>
+        <v>-9.21603348296609</v>
       </c>
       <c r="M12" t="n">
-        <v>25.07826121722721</v>
+        <v>27.24730670837919</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.06999568359145</v>
+        <v>-3.378345005747541</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>27.26998042233406</v>
+        <v>26.08865071076689</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.297941764772838</v>
+        <v>-7.487054217138677</v>
       </c>
       <c r="R12" t="n">
-        <v>25.58937452880411</v>
+        <v>27.82881724051246</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.257537131900296</v>
+        <v>-1.316250920168582</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>27.78464260916596</v>
+        <v>26.57622286373023</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.472898549056889</v>
+        <v>-5.758074951311243</v>
       </c>
       <c r="W12" t="n">
-        <v>26.10048784038101</v>
+        <v>28.41032777264572</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.445078580209163</v>
+        <v>0.7458431654103537</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>28.04197370258191</v>
+        <v>26.8200089402119</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.5603769411989146</v>
+        <v>-4.89358531839753</v>
       </c>
       <c r="AB12" t="n">
-        <v>26.35604449616946</v>
+        <v>28.70108303871235</v>
       </c>
       <c r="AC12" t="n">
-        <v>-6.538849304363604</v>
+        <v>1.776890208199822</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>5.661854304930773</v>
+        <v>5.606715637027309</v>
       </c>
       <c r="AF12" t="n">
-        <v>5.992096184315594</v>
+        <v>6.268795332990802</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>elevated</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="F13" t="n">
-        <v>14.25095603772536</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-10.9315247642165</v>
-      </c>
-      <c r="H13" t="n">
-        <v>13.91693867149296</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-13.01913330316902</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>14.46829219353633</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-9.573173790397927</v>
-      </c>
-      <c r="M13" t="n">
-        <v>14.11184928149075</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-11.80094199068279</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>14.90296450515828</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-6.856471842760747</v>
-      </c>
-      <c r="R13" t="n">
-        <v>14.50167050148635</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-9.364559365710335</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>15.33763681678023</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-4.139769895123568</v>
-      </c>
-      <c r="W13" t="n">
-        <v>14.89149172148194</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-6.928176740737902</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="Z13" t="n">
-        <v>15.55497297259121</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-2.781418921304968</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>15.08640233147973</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-5.709985428251684</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="AE13" t="n">
-        <v>8.750050598419486</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>8.064337552469622</v>
-      </c>
-      <c r="AG13" t="b">
+      <c r="F13" s="2" t="n">
+        <v>14.22932528426003</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-11.06671697337482</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>14.49529777915446</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>-9.404388880284609</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>14.44627180359814</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>-9.710801227511624</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>14.68760444475485</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>-8.202472220282209</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>14.88016484227437</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>-6.998969735785209</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>15.07221777595561</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>-5.798638900277442</v>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>15.31405788095059</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>-4.287138244058797</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>15.45683110715637</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>-3.394805580272697</v>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>15.5310044002887</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>-2.931222498195596</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>15.64913777275675</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>-2.192888920270308</v>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>8.747746613200293</v>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>7.655409514072869</v>
+      </c>
+      <c r="AG13" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>late-cycle/peak</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>55.9353517496054</v>
+      </c>
+      <c r="G14" t="n">
+        <v>50.60676292300861</v>
+      </c>
+      <c r="H14" t="n">
+        <v>65.43379972239016</v>
+      </c>
+      <c r="I14" t="n">
+        <v>76.18147475064663</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>56.53657639519886</v>
+      </c>
+      <c r="L14" t="n">
+        <v>52.22556918470345</v>
+      </c>
+      <c r="M14" t="n">
+        <v>66.22537848339563</v>
+      </c>
+      <c r="N14" t="n">
+        <v>78.3128122870103</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>57.73902568638581</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>55.46318170809319</v>
+      </c>
+      <c r="R14" t="n">
+        <v>67.80853600540658</v>
+      </c>
+      <c r="S14" t="n">
+        <v>82.57548735973769</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>58.94147497757275</v>
+      </c>
+      <c r="V14" t="n">
+        <v>58.70079423148291</v>
+      </c>
+      <c r="W14" t="n">
+        <v>69.39169352741752</v>
+      </c>
+      <c r="X14" t="n">
+        <v>86.83816243246503</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>59.54269962316621</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>60.31960049317775</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>70.18327228842298</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>88.9694999688287</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>6.247677079198429</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>7.004239946507814</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19.04447508546572</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10.40275411864184</v>
+      </c>
+      <c r="H15" t="n">
+        <v>19.07021653853896</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.55197993355921</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>19.36216556353057</v>
+      </c>
+      <c r="L15" t="n">
+        <v>12.24443804945257</v>
+      </c>
+      <c r="M15" t="n">
+        <v>19.4016289921046</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12.47321154843248</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>19.99754651966026</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15.92780591107399</v>
+      </c>
+      <c r="R15" t="n">
+        <v>20.06445389923588</v>
+      </c>
+      <c r="S15" t="n">
+        <v>16.31567477817901</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>20.63292747578997</v>
+      </c>
+      <c r="V15" t="n">
+        <v>19.61117377269546</v>
+      </c>
+      <c r="W15" t="n">
+        <v>20.72727880636716</v>
+      </c>
+      <c r="X15" t="n">
+        <v>20.15813800792557</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>20.95061795385482</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>21.45285770350618</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>21.0586912599328</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>22.07936962279884</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.531883656403082</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>9.91043529706813</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>24.93705299334903</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>-8.319658112687399</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>24.41266766621246</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-10.24754534480713</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>25.29238089982259</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>-7.013305515358137</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>24.77220108274257</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>-8.925731313446416</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>26.0030367127697</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>-4.400600320699633</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>25.49126791580279</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>-6.282103250725024</v>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>26.71369252571682</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>-1.787895126041117</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>26.21033474886302</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>-3.63847518800362</v>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>27.06902043219037</v>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>-0.4815425287118646</v>
+      </c>
+      <c r="AB16" s="2" t="n">
+        <v>26.56986816539312</v>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>-2.316661156642918</v>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>8.198917158757716</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>8.462507656762542</v>
+      </c>
+      <c r="AG16" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>mid-cycle</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>23.98663465396584</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>-0.05568894180901784</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>23.96383492181299</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-0.1506878257791944</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>24.42410419368611</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>1.767100807025446</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>24.31633878768207</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>1.318078282008606</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>25.29904327312664</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>5.412680304694351</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>25.02134651942021</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>4.255610497584184</v>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>26.17398235256717</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>9.05825980236321</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>25.72635425115835</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>7.193142713159784</v>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>26.61145189228744</v>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>10.88104955119766</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>26.07885811702741</v>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>8.66190882094755</v>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="n">
+        <v>10.37516403282238</v>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>8.452875202271205</v>
+      </c>
+      <c r="AG17" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>late-cycle/peak</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16.21431509706036</v>
+      </c>
+      <c r="G18" t="n">
+        <v>32.90422210705215</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17.56363498831108</v>
+      </c>
+      <c r="I18" t="n">
+        <v>43.96422121566464</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>16.37961297693776</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34.25912276178493</v>
+      </c>
+      <c r="M18" t="n">
+        <v>17.75968961788529</v>
+      </c>
+      <c r="N18" t="n">
+        <v>45.57122637610891</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>16.71020873669256</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>36.96892407125054</v>
+      </c>
+      <c r="R18" t="n">
+        <v>18.15179887703369</v>
+      </c>
+      <c r="S18" t="n">
+        <v>48.7852366969975</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>17.04080449644736</v>
+      </c>
+      <c r="V18" t="n">
+        <v>39.67872538071611</v>
+      </c>
+      <c r="W18" t="n">
+        <v>18.5439081361821</v>
+      </c>
+      <c r="X18" t="n">
+        <v>51.99924701788605</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>17.20610237632476</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>41.03362603544889</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>18.7399627657563</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>53.60625217833033</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>5.935217775506421</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>6.480502485808986</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.046171869537905</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-26.39669534036314</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.878107832403921</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-32.44216430201724</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>2.073894249780087</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-25.39948741798249</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.904801879817548</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-31.48194676915295</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>2.129339010264451</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-23.40507157322118</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.958189974644803</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-29.56151170342436</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>2.184783770748815</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-21.41065572845989</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.011578069472058</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-27.64107663769577</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.212506150990997</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-20.41344780607924</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.038272116885685</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-26.68085910483148</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>7.81154530355571</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>8.179200514537229</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>32.83444825163468</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-15.78751410198851</v>
+      </c>
+      <c r="H20" t="n">
+        <v>30.59290196827169</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-21.53654278463276</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>33.29922249379609</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-14.59547962606799</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30.98125822578994</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-20.54050211390116</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>34.22877097811892</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-12.21141067422693</v>
+      </c>
+      <c r="R20" t="n">
+        <v>31.75797074082645</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-18.54842077243794</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>35.15831946244175</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-9.827341722385864</v>
+      </c>
+      <c r="W20" t="n">
+        <v>32.53468325586296</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-16.55633943097472</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>35.62309370460316</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-8.63530724646534</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>32.92303951338121</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-15.56029876024311</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>8.147080287373305</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7.337173914937892</v>
+      </c>
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
     </row>
